--- a/r5-aist-trustworthyai-poc-pipeline/StructureDefinition-eu-ai-machine-execution-audit-event.xlsx
+++ b/r5-aist-trustworthyai-poc-pipeline/StructureDefinition-eu-ai-machine-execution-audit-event.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>EU AI Act Machine Execution Audit Event</t>
+    <t>EU AI Execution Audit Event</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T09:07:35+00:00</t>
+    <t>2026-06-18T11:52:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Logs the automated execution of an AI model, establishing the core traceability chain.</t>
+    <t>An AuditEvent profile documenting execution-related metadata of an AI-supported processing event to support retrospective reconstruction and auditability.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -7760,7 +7760,7 @@
         <v>78</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>18</v>
@@ -11349,7 +11349,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
         <v>505</v>
       </c>
@@ -11370,7 +11370,7 @@
         <v>78</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>18</v>
